--- a/VerveStacks_VNM_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_VNM_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD94A1A3-5B9C-465D-9007-39CAA7D910BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04AD5FE-7C08-4ABA-B3A1-E9BFFAC0FADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8876" uniqueCount="3325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8866" uniqueCount="3322">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -10095,15 +10095,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_VN1003-500,e_VN1005-500,e_VN1008-500,e_VN1010-500,e_VN1014-500,e_VN1016-500,e_VN1019-500,e_VN1020-500,e_VN1022-500,e_VN1024-220,e_VN1130-500,e_VN1133-220,e_VN1134-220,e_VN1137-500,e_VN1138-220,e_VN1139-220,e_VN1140-500,e_VN1141-220,e_VN1141-500,e_VN1142-500,e_VN1145-220,e_VN1146-500,e_VN1147-220,e_VN1149-500,e_VN1153-220,e_VN1154-220,e_VN1157-220,e_VN1178-500,e_VN1179-220,e_VN1184-500,e_VN1187-500,e_VN1188-220,e_VN1191-500,e_VN1192-500,e_VN1196-500,e_VN1198-500,e_VN1206-220,e_VN1208-500,e_VN1209-500,e_VN1210-500,e_VN1213-220,e_VN1218-220,e_VN1219-220,e_VN1223-220,e_VN1223-500,e_VN1224-500,e_VN1226-500,e_VN1228-220,e_VN181-500,e_VN183-500,e_VN186-500,e_VN188-500,e_VN189-500,e_VN192-500,e_VN195-220,e_VN195-500,e_VN196-500,e_VN197-500,e_VN198-500,e_VN199-500,e_VN2-220,e_VN200-500,e_VN201-500,e_VN202-500,e_VN203-220,e_VN203-500,e_VN205-500,e_VN206-500,e_VN207-500,e_VN209-220,e_VN210-500,e_VN211-500,e_VN212-500,e_VN213-500,e_VN214-500,e_VN215-500,e_VN216-500,e_VN217-500,e_VN218-500,e_VN224-500,e_VN225-500,e_VN226-500,e_VN229-500,e_VN230-220,e_VN230-500,e_VN232-220,e_VN251-220,e_VN252-220,e_VN274-220,e_VN310-220,e_VN323-500,e_VN328-500,e_VN334-500,e_VN365-220,e_VN383-220,e_VN391-500,e_VN392-500,e_VN393-500,e_VN394-500,e_VN395-500,e_VN396-500,e_VN397-500,e_VN398-500,e_VN400-500,e_VN401-500,e_VN402-500,e_VN404-500,e_VN405-500,e_VN406-500,e_VN408-220,e_VN408-500,e_VN409-500,e_VN410-220,e_VN411-500,e_VN412-500,e_VN413-220,e_VN414-500,e_VN418-500,e_VN419-500,e_VN421-500,e_VN422-500,e_VN427-500,e_VN428-500,e_VN429-500,e_VN430-500,e_VN431-500,e_VN432-500,e_VN433-500,e_VN434-500,e_VN435-500,e_VN436-500,e_VN437-500,e_VN438-500,e_VN439-500,e_VN440-500,e_VN441-500,e_VN442-500,e_VN449-500,e_VN451-220,e_VN452-500,e_VN454-500,e_VN455-500,e_VN509-500,e_VN511-220,e_VN511-500,e_VN512-500,e_VN513-500,e_VN514-500,e_VN515-500,e_VN516-500,e_VN517-500,e_VN518-500,e_VN519-220,e_VN519-500,e_VN520-500,e_VN521-220,e_VN521-500,e_VN522-500,e_VN523-500,e_VN524-500,e_VN525-500,e_VN526-500,e_VN527-500,e_VN528-500,e_VN529-500,e_VN533-220,e_VN534-220,e_VN534-500,e_VN536-220,e_VN537-220,e_VN538-220,e_VN539-220,e_VN540-220,e_VN589-500,e_VN592-500,e_VN595-500,e_VN597-500,e_VN598-500,e_VN624-220,e_VN801-500,e_VN802-500,e_VN803-500,e_VN805-500,e_VN806-500,e_VN807-500,e_VN813-500,e_VN814-500,e_VN815-500,e_VN819-500,e_VN823-500,e_VN824-500,e_VN825-500,e_VN826-500,e_VN836-220,e_VN837-220,e_VN902-220,e_VN937-220,e_VN988-220,e_VN994-500,e_VN998-500,e_VN999-500,e_w1018528434-220,e_w1044469623-220,e_w1045125739-220,e_w1047280375-220,e_w1047400696-220,e_w1047400696-500,e_w1052065872-220,e_w1052125064-220,e_w1087113517-220,e_w1091686589-220,e_w1091782693-220,e_w1176845159-220,e_w1176845164-220,e_w1183902227-500,e_w1216970886-220,e_w1216970886-500,e_w1245195233-220,e_w1258175914-220,e_w1265274413-220,e_w1265274426-500,e_w1265612937-220,e_w1272088369-220,e_w1273255946-220,e_w1273527149-220,e_w1273527210-220,e_w1273948701-220,e_w1274076450-220,e_w1274076450-500,e_w1274466549-220,e_w1320784083-220,e_w1320784083-500,e_w1374565925-220,e_w1376430795-220,e_w1376430795-500,e_w241065371-220,e_w306295536-220,e_w306295536-500,e_w306295540-220,e_w307638314-220,e_w315766007-220,e_w315766015-220,e_w400645442-220,e_w400791086-220,e_w400791086-500,e_w401042494-220,e_w401532710-220,e_w468821783-220,e_w468821783-500,e_w548717060-220,e_w548717060-500,e_w548723124-220,e_w548752026-220,e_w548869165-220,e_w548869165-230,e_w548970118-220,e_w549038673-220,e_w549296358-220,e_w549380074-220,e_w549400050-220,e_w549400050-500,e_w549400051-220,e_w549577079-220,e_w549914200-220,e_w549941525-220,e_w549959350-220,e_w549959354-220,e_w630750798-220,e_w630750798-500,e_w715041211-220,e_w744217936-220,e_w762471641-220,e_w827889590-500,e_w827889600-220,e_w827889600-500,e_w967849373-220</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -11326,10 +11317,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0141905F-6D81-4685-8D8A-C999381C7431}">
-  <dimension ref="B2:AJ1719"/>
+  <dimension ref="B2:AF1719"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -11342,11 +11333,8 @@
       <c r="U2" t="s">
         <v>2009</v>
       </c>
-      <c r="AH2" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -11398,17 +11386,8 @@
       <c r="AA3" t="s">
         <v>1851</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>1852</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>135</v>
       </c>
@@ -11475,17 +11454,8 @@
       <c r="AF4" t="s">
         <v>3319</v>
       </c>
-      <c r="AH4" t="s">
-        <v>3322</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>3323</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>136</v>
       </c>
@@ -11549,17 +11519,8 @@
       <c r="AF5" t="s">
         <v>3320</v>
       </c>
-      <c r="AH5" t="s">
-        <v>3324</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>3323</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>137</v>
       </c>
@@ -11624,7 +11585,7 @@
         <v>3321</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>138</v>
       </c>
@@ -11674,7 +11635,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>139</v>
       </c>
@@ -11724,7 +11685,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>140</v>
       </c>
@@ -11774,7 +11735,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>141</v>
       </c>
@@ -11824,7 +11785,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>142</v>
       </c>
@@ -11874,7 +11835,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>143</v>
       </c>
@@ -11924,7 +11885,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>144</v>
       </c>
@@ -11974,7 +11935,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>145</v>
       </c>
@@ -12024,7 +11985,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>146</v>
       </c>
@@ -12074,7 +12035,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>147</v>
       </c>

--- a/VerveStacks_VNM_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_VNM_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04AD5FE-7C08-4ABA-B3A1-E9BFFAC0FADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{507EDFA6-F0A4-446C-AF4B-3119B6932760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11316,7 +11316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0141905F-6D81-4685-8D8A-C999381C7431}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEDD5FE-D5D2-43CA-AFD7-42D6826BF0FE}">
   <dimension ref="B2:AF1719"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -52505,7 +52505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A56BA8-FF49-47FD-9C67-40669A4794D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14040288-ED53-4E25-A7BB-0914B2DDA0B7}">
   <dimension ref="B9:L29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_VNM_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_VNM_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{287995D7-065E-4D2B-9E6B-8462CF60A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6895DE89-DA3A-4C61-B8EE-F05A7B03CE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10589,7 +10589,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C458F064-A41F-4AF0-A8E6-8152133CE490}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59A961DD-3119-46CA-B2F6-DA35B0ECD025}">
   <dimension ref="B2:AF1719"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -51778,7 +51778,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73C4E1D-2D3B-42BB-9C55-C61DDE656F8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3FA7ADE-5B12-425C-B795-CABA344D472E}">
   <dimension ref="B9:L29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
